--- a/QLDA.WebApi/PrintTemplates/Import_DeXuatChuTruongChuyenTiep.xlsx
+++ b/QLDA.WebApi/PrintTemplates/Import_DeXuatChuTruongChuyenTiep.xlsx
@@ -1,47 +1,163 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SER\QLDA.WebApi\PrintTemplates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE89A32-63EE-4C12-8F08-CF5D4EA31D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Danh sach" sheetId="1" r:id="rId1"/>
+    <sheet name="Danh mục" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+  <si>
+    <t>MẪU IMPORT ĐỀ XUẤT CHỦ TRƯƠNG CHUYỂN TIẾP</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Số liệu giải ngân</t>
+  </si>
+  <si>
+    <t>Ước giải ngân</t>
+  </si>
+  <si>
+    <t>Nhu cầu kinh phí</t>
+  </si>
+  <si>
+    <t>Khối lượng đã hoàn thành</t>
+  </si>
+  <si>
+    <t>Khối lượng dự kiến hoàn thành</t>
+  </si>
+  <si>
+    <t>1, 2, 3...</t>
+  </si>
+  <si>
+    <t>Nhập số tiền (đồng)</t>
+  </si>
+  <si>
+    <t>Mô tả khối lượng</t>
+  </si>
+  <si>
+    <t>Dự án</t>
+  </si>
+  <si>
+    <t>Bước</t>
+  </si>
+  <si>
+    <t>$cbo1</t>
+  </si>
+  <si>
+    <t>$cbo2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ỦY BAN NHÂN DÂN THÀNH PHỐ HỒ CHÍ MINH
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>TRUNG TÂM CHUYỂN ĐỔI SỐ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Độc lập - Tự do - Hạnh phúc</t>
+    </r>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -49,107 +165,213 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DeXuatChuyenTiepImport" displayName="DeXuatChuyenTiepImport" ref="A6:F8" headerRowCount="1">
-  <autoFilter ref="A6:F8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DeXuatChuyenTiepImport" displayName="DeXuatChuyenTiepImport" ref="A5:F7" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+  <autoFilter ref="A5:F7" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Số liệu giải ngân"/>
-    <tableColumn id="3" name="Ước giải ngân"/>
-    <tableColumn id="4" name="Nhu cầu kinh phí"/>
-    <tableColumn id="5" name="Khối lượng đã hoàn thành"/>
-    <tableColumn id="6" name="Khối lượng dự kiến hoàn thành"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Số liệu giải ngân" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ước giải ngân" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nhu cầu kinh phí" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Khối lượng đã hoàn thành" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Khối lượng dự kiến hoàn thành" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="C3:C4">
+  <autoFilter ref="C3:C4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="1">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Dự án"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="E3:E4">
+  <autoFilter ref="E3:E4" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="1">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Bước"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -439,100 +661,248 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="8" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="40.77734375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="37.88671875" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MAU IMPORT DE XUAT CHU TRUONG CHUYEN TIEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Số liệu giải ngân</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Ước giải ngân</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nhu cầu kinh phí</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Khối lượng đã hoàn thành</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Khối lượng dự kiến hoàn thành</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>1, 2, 3...</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Nhập số tiền (đồng)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Nhập số tiền (đồng)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Nhập số tiền (đồng)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Mô tả khối lượng</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Mô tả khối lượng</t>
-        </is>
-      </c>
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="C3:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/QLDA.WebApi/PrintTemplates/Import_DeXuatChuTruongChuyenTiep.xlsx
+++ b/QLDA.WebApi/PrintTemplates/Import_DeXuatChuTruongChuyenTiep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SER\QLDA.WebApi\PrintTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE89A32-63EE-4C12-8F08-CF5D4EA31D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F975A720-6C94-4DD0-8BEC-C05F5ADB4F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,16 +17,25 @@
     <sheet name="Danh mục" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+  <si>
+    <t>ỦY BAN NHÂN DÂN THÀNH PHỐ HỒ CHÍ MINH
+TRUNG TÂM CHUYỂN ĐỔI SỐ</t>
+  </si>
+  <si>
+    <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM
+Độc lập - Tự do - Hạnh phúc</t>
+  </si>
   <si>
     <t>MẪU IMPORT ĐỀ XUẤT CHỦ TRƯƠNG CHUYỂN TIẾP</t>
   </si>
   <si>
-    <t>STT</t>
+    <t>Dự án</t>
   </si>
   <si>
     <t>Số liệu giải ngân</t>
@@ -44,7 +53,7 @@
     <t>Khối lượng dự kiến hoàn thành</t>
   </si>
   <si>
-    <t>1, 2, 3...</t>
+    <t>$cbo1</t>
   </si>
   <si>
     <t>Nhập số tiền (đồng)</t>
@@ -53,46 +62,13 @@
     <t>Mô tả khối lượng</t>
   </si>
   <si>
-    <t>Dự án</t>
-  </si>
-  <si>
     <t>Bước</t>
   </si>
   <si>
-    <t>$cbo1</t>
-  </si>
-  <si>
     <t>$cbo2</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ỦY BAN NHÂN DÂN THÀNH PHỐ HỒ CHÍ MINH
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>TRUNG TÂM CHUYỂN ĐỔI SỐ</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Độc lập - Tự do - Hạnh phúc</t>
-    </r>
+    <t>Chọn từ danh sách</t>
   </si>
 </sst>
 </file>
@@ -132,16 +108,16 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -189,26 +165,32 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -219,11 +201,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -231,11 +211,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -243,11 +221,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -255,11 +231,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -267,11 +241,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -279,11 +251,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -291,11 +261,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -303,11 +271,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -315,11 +281,9 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <name val="Times New Roman"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
     </dxf>
   </dxfs>
@@ -336,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DeXuatChuyenTiepImport" displayName="DeXuatChuyenTiepImport" ref="A5:F7" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DeXuatChuyenTiepImport" displayName="DeXuatChuyenTiepImport" ref="A5:F7" headerRowDxfId="8" dataDxfId="7" totalsRowDxfId="6">
   <autoFilter ref="A5:F7" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -346,12 +310,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Số liệu giải ngân" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ước giải ngân" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nhu cầu kinh phí" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Khối lượng đã hoàn thành" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Khối lượng dự kiến hoàn thành" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Số liệu giải ngân" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ước giải ngân" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nhu cầu kinh phí" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Khối lượng đã hoàn thành" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Khối lượng dự kiến hoàn thành" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -665,204 +629,207 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="6" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="40.77734375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="37.88671875" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="47.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40.77734375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="37.88671875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -870,6 +837,7 @@
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -884,15 +852,15 @@
   <sheetData>
     <row r="3" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>

--- a/QLDA.WebApi/PrintTemplates/Import_DeXuatChuTruongChuyenTiep.xlsx
+++ b/QLDA.WebApi/PrintTemplates/Import_DeXuatChuTruongChuyenTiep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SER\QLDA.WebApi\PrintTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F975A720-6C94-4DD0-8BEC-C05F5ADB4F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6298776-CEBA-471C-B81B-9F5299B4B874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,11 @@
     <sheet name="Danh mục" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>ỦY BAN NHÂN DÂN THÀNH PHỐ HỒ CHÍ MINH
 TRUNG TÂM CHUYỂN ĐỔI SỐ</t>
@@ -38,6 +37,9 @@
     <t>Dự án</t>
   </si>
   <si>
+    <t>Năm</t>
+  </si>
+  <si>
     <t>Số liệu giải ngân</t>
   </si>
   <si>
@@ -53,29 +55,32 @@
     <t>Khối lượng dự kiến hoàn thành</t>
   </si>
   <si>
+    <t>Chọn từ danh sách</t>
+  </si>
+  <si>
+    <t>Nhập năm (VD: 2026)</t>
+  </si>
+  <si>
+    <t>Nhập số tiền (đồng)</t>
+  </si>
+  <si>
+    <t>Mô tả khối lượng</t>
+  </si>
+  <si>
     <t>$cbo1</t>
   </si>
   <si>
-    <t>Nhập số tiền (đồng)</t>
-  </si>
-  <si>
-    <t>Mô tả khối lượng</t>
-  </si>
-  <si>
     <t>Bước</t>
   </si>
   <si>
     <t>$cbo2</t>
-  </si>
-  <si>
-    <t>Chọn từ danh sách</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,10 +119,17 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -167,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -188,105 +200,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -300,22 +222,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DeXuatChuyenTiepImport" displayName="DeXuatChuyenTiepImport" ref="A5:F7" headerRowDxfId="8" dataDxfId="7" totalsRowDxfId="6">
-  <autoFilter ref="A5:F7" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DeXuatChuyenTiepImport" displayName="DeXuatChuyenTiepImport" ref="A5:G7">
+  <autoFilter ref="A5:G7" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
     <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Số liệu giải ngân" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ước giải ngân" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nhu cầu kinh phí" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Khối lượng đã hoàn thành" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Khối lượng dự kiến hoàn thành" dataDxfId="0"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Dự án"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Năm"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Số liệu giải ngân"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Ước giải ngân"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nhu cầu kinh phí"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Khối lượng đã hoàn thành"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Khối lượng dự kiến hoàn thành"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -626,40 +550,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="37.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="24.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29" style="3" customWidth="1"/>
     <col min="6" max="6" width="37.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="3"/>
+    <col min="7" max="7" width="31.77734375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
       <c r="E1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
@@ -669,19 +596,19 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -696,148 +623,153 @@
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:F2"/>
+    <mergeCell ref="E1:G2"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -855,15 +787,15 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
